--- a/input_format/output_format.xlsx
+++ b/input_format/output_format.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/77c4881169651c74/Desktop/Nokia_Router_Tool/input_format/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{971DA30D-4383-4CC9-B3A7-1B03FCAFAE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5DEAF9D-91C5-4497-AFF5-49769555E35F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{971DA30D-4383-4CC9-B3A7-1B03FCAFAE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BE90B637-28B5-4227-80A9-F06756681963}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="25">
   <si>
     <t>site_id</t>
   </si>
@@ -61,6 +61,24 @@
     <t>target_port:target_vlan</t>
   </si>
   <si>
+    <t>configure service vprn "extracted_vrf"</t>
+  </si>
+  <si>
+    <t>interface "extracted_interface_line" shutdown</t>
+  </si>
+  <si>
+    <t>interface "extracted_interface_line" sap parent_port:src_vlan shutdown</t>
+  </si>
+  <si>
+    <t>interface "extracted_interface_line" no sap parent_port:src_vlan</t>
+  </si>
+  <si>
+    <t>no interface "extracted_interface_line"</t>
+  </si>
+  <si>
+    <t>exit all</t>
+  </si>
+  <si>
     <t>parent_port:src_vlan</t>
   </si>
   <si>
@@ -70,6 +88,9 @@
     <t>"vlan deletion from target_router"</t>
   </si>
   <si>
+    <t>"vlan configuration in parent_router as per config logs"</t>
+  </si>
+  <si>
     <t>"vlan deletion mop from parent_router"</t>
   </si>
   <si>
@@ -89,12 +110,6 @@
   </si>
   <si>
     <t>target_port configuration model wise</t>
-  </si>
-  <si>
-    <t>"vlan deletion from parent router"</t>
-  </si>
-  <si>
-    <t>"vlan configuration in parent_router as per input configuration logs"</t>
   </si>
 </sst>
 </file>
@@ -492,14 +507,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E37DCBAF-1412-48D7-8B54-C2E1151895EF}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="61.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="58.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="47.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
@@ -524,33 +539,94 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>18</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3"/>
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E3" t="s">
-        <v>19</v>
+      <c r="B4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -574,32 +650,32 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
@@ -609,32 +685,32 @@
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
